--- a/PurgeRefactor_Tracker_20260405.xlsx
+++ b/PurgeRefactor_Tracker_20260405.xlsx
@@ -56,7 +56,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -78,11 +78,25 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,6 +112,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -891,6 +911,222 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>lsp_DbPurgeHistoryData: #BlkOfRxsToDel temp table dropped and recreated every iteration</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Every pass through the OeOrderHistory WHILE loop (lines 138-152) drops #BlkOfRxsToDel, recreates it, and rebuilds a nonclustered index. This forces SQL Server to recompile all ~40 downstream DELETE statements that join to #BlkOfRxsToDel on every single iteration. Plan compilation is CPU-intensive, generates tempdb allocation/deallocation churn, and prevents plan caching. At 100K-row block sizes against millions of history rows, the loop may execute dozens of times per driver call.</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Create #BlkOfRxsToDel once before the WHILE loop with the index already in place. Replace the DROP/CREATE/INDEX sequence inside the loop with TRUNCATE TABLE #BlkOfRxsToDel at the top of each iteration. The ~40 downstream DELETE plans get compiled once and reused across all iterations.</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Eliminate dozens of plan recompilations per iteration; reduce CPU overhead and tempdb contention; plans cached and reused across loop iterations. Likely the single highest-impact fix in the purge process.</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>lsp_DbPurgeHistoryData: WHILE EXISTS(SELECT * FROM OeOrderHistory...) redundant table probe per iteration</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>The main loop (line 130) evaluates WHILE EXISTS(SELECT * FROM OeOrderHistory WHERE HistoryDtTm &lt; @cutoff) on every iteration before populating #BlkOfRxsToDel. This is a redundant seek/scan against a potentially massive table (OeOrderHistory) when the previous iteration's DELETE already tells us whether rows remain. Each probe reads the clustered index to check for qualifying rows — wasted I/O when the loop could simply check if the last batch was empty.</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Replace WHILE EXISTS(...) with a @@ROWCOUNT-based termination pattern: after the INSERT INTO #BlkOfRxsToDel, check IF @@ROWCOUNT = 0 BREAK. This eliminates one full table probe per iteration. Consistent with the v3 pattern used in lsp_DbDeleteOldEvents.</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Eliminate one clustered index seek/scan against OeOrderHistory per loop iteration; reduce total reads proportional to number of iterations. Simple, risk-free change.</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>lsp_DbPurgeHistoryData: Cascade temp tables (#ShpIds, #ManIds, #PalIds, #Grps, #Pats, etc.) are unindexed heaps</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>During each iteration, the proc populates ~8 cascade temp tables (#ShpIds, #ManIds, #PalIds, #Grps, #Pats, #Prescrs, #RxPats, #GrpPats) to drive orphan detection and cascade deletes. These tables are heaps — no clustered index, no PK. Every downstream DELETE that joins to one of these tables performs a heap scan on the temp table side. If a single iteration yields 15K shipment IDs, every DELETE joining #ShpIds scans all 15K rows. Multiplied across ~40 DELETE statements per iteration, the wasted reads add up significantly.</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Add a clustered index or PRIMARY KEY to each cascade temp table after population (or define it at CREATE). For example: CREATE TABLE #ShpIds (ShpId INT PRIMARY KEY CLUSTERED). This converts downstream join scans to seeks. Alternatively, use INSERT INTO ... WITH (TABLOCK) followed by CREATE CLUSTERED INDEX for bulk-load efficiency.</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Convert heap scans to index seeks across ~40 DELETE joins per iteration; reduce logical reads proportional to cascade table size × number of downstream joins. Second-highest impact fix after #BlkOfRxsToDel recompilation.</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>lsp_DbDeleteOldSmartShelfErrors / Events: WHILE condition bug (&gt; instead of &lt;) prevents loop execution</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Both procs use WHILE @DeletedCount &gt; @MaxToDelete as the loop condition. Since @DeletedCount starts at 0 and @MaxToDelete is a large number, the condition is immediately false and the loop body never executes. These tables are never purged, growing unbounded. This is a correctness bug with performance implications — unbounded table growth degrades every query that touches these tables.</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Change WHILE @DeletedCount &gt; @MaxToDelete to WHILE @DeletedCount &lt; @MaxToDelete in both lsp_DbDeleteOldSmartShelfErrors and lsp_DbDeleteOldSmartShelfEvents. Verify in dev before deploying — first execution will purge accumulated backlog.</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Tables actually get purged; prevents unbounded growth; all queries touching SmartShelf.EvtErrorLog and SmartShelf.EvtEventLog benefit from reduced table size. First execution may be long due to backlog.</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>lsp_DbDeleteOldDiagEvents: Double-delete bug — DELETE TOP + self-join delete in same pass</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>The proc executes a DELETE TOP(@BlockSize) followed by a self-join DELETE against the same rows in the same transaction. The second DELETE seeks rows that were already removed by the first, finding nothing but still consuming I/O for the seek operations and holding locks longer than necessary. Additionally, the proc has no @MaxToDelete guard, no TRY/CATCH, and uses legacy @@Error handling.</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Remove the redundant second DELETE statement. Add @MaxToDelete parameter with @@ROWCOUNT-based loop termination. Add TRY/CATCH with proper error logging. Replace legacy @@Error pattern.</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Eliminate wasted seeks from redundant delete; reduce lock hold time; add safety bounds and error handling. Moderate IOP impact, high reliability impact.</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>lsp_DbPurgeHistoryData: No TRY/CATCH error handling in main proc</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>The main 1,619-line purge procedure has no TRY/CATCH anywhere. If any of the ~40 DELETE statements fail mid-iteration (deadlock, timeout, constraint violation), execution continues to the next statement with no rollback, no logging, and no notification to the driver proc. This can leave orphaned partial deletes that subsequent runs trip over repeatedly, potentially causing cascading failures.</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Wrap the main loop body in TRY/CATCH with proper error logging to the event table. On CATCH, log the error, clean up temp tables, and RETURN with an error output parameter so the driver proc knows to stop. Consistent with pattern in lsp_DbDeleteOldEvents (v3).</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Prevent silent partial-delete failures; enable driver proc to detect and halt on errors; reduce orphaned data scenarios. Reliability improvement, not direct IOP reduction.</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
